--- a/tests/testdata/excel/外部リンク.xlsx
+++ b/tests/testdata/excel/外部リンク.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FFF4371-8E3B-4A1D-9EA4-50146DD9828A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C5EE083-51A4-4A8D-ABF7-AB0808FA5DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{746F4057-510C-414B-94C4-C049F104E7AC}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{3376F341-3E3C-4EB5-B3B4-67817F416F4F}"/>
   </bookViews>
   <sheets>
     <sheet name="リンク" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6041F5BA-1814-4F18-9358-189067A420E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF1797A-56C0-40A8-A433-82A99DA2743E}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/外部リンク.xlsx
+++ b/tests/testdata/excel/外部リンク.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C5EE083-51A4-4A8D-ABF7-AB0808FA5DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{884B0312-94D4-494F-AD63-53D095D9E55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{3376F341-3E3C-4EB5-B3B4-67817F416F4F}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{58987DDB-4A82-4BA8-9286-0E0ED6607445}"/>
   </bookViews>
   <sheets>
     <sheet name="リンク" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF1797A-56C0-40A8-A433-82A99DA2743E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D4AD7A-F3D7-4AE5-A139-A2890A7CAB26}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
